--- a/docs/use-cases/dist/HL7_BH_USE_CASES-ED-Scenario-11.xlsx
+++ b/docs/use-cases/dist/HL7_BH_USE_CASES-ED-Scenario-11.xlsx
@@ -2971,7 +2971,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="116" customHeight="1">
+    <row r="35" ht="172" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.7-2A</t>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPiER Caring Contact (built — spier-caring-contact) — TL-010 is built and launchable at /patient/workflow/caring-contact; gap — no PlanDefinition schedules the series, and the ED-SAFE telephone protocol (TL-012) it would envelope is not modelled</t>
+          <t xml:space="preserve">SPiER Caring Contact (built — spier-caring-contact) — TL-010 is built and launchable at /patient/workflow/caring-contact, and each follow-up call is recordable as a SPiER Follow-Up Outreach Attempt (built — spier-outreach-attempt, TL-033); gap — no PlanDefinition schedules the series: neither the caring-contact cadence (#628) nor the ED-SAFE telephone-call protocol it would envelope</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">

--- a/docs/use-cases/dist/HL7_BH_USE_CASES-ED-Scenario-11.xlsx
+++ b/docs/use-cases/dist/HL7_BH_USE_CASES-ED-Scenario-11.xlsx
@@ -2971,7 +2971,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="172" customHeight="1">
+    <row r="35" ht="228" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.7-2A</t>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPiER Caring Contact (built — spier-caring-contact) — TL-010 is built and launchable at /patient/workflow/caring-contact, and each follow-up call is recordable as a SPiER Follow-Up Outreach Attempt (built — spier-outreach-attempt, TL-033); gap — no PlanDefinition schedules the series: neither the caring-contact cadence (#628) nor the ED-SAFE telephone-call protocol it would envelope</t>
+          <t xml:space="preserve">SPiER Caring Contact (built — spier-caring-contact) — TL-010 is built and launchable at /patient/workflow/caring-contact, each follow-up call is recordable as a SPiER Follow-Up Outreach Attempt (built — spier-outreach-attempt, TL-033), and the caring-contact series is scheduled by the SPiER Caring Contact Schedule (built — SPiERCaringContactSchedule), offsets from the care transition that the published pathway's post-transition step references; gap — no PlanDefinition schedules the ED-SAFE telephone-call protocol</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
